--- a/Vocab/dongtubatquytac.xlsx
+++ b/Vocab/dongtubatquytac.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="70">
   <si>
     <t>sein</t>
   </si>
@@ -219,6 +219,21 @@
   </si>
   <si>
     <t>đi ra ngoài</t>
+  </si>
+  <si>
+    <t>tragen</t>
+  </si>
+  <si>
+    <t>trage</t>
+  </si>
+  <si>
+    <t>trägst</t>
+  </si>
+  <si>
+    <t>trägt</t>
+  </si>
+  <si>
+    <t>mang, mặc</t>
   </si>
 </sst>
 </file>
@@ -536,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.5703125" customWidth="1"/>
@@ -861,6 +876,32 @@
         <v>64</v>
       </c>
     </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" t="s">
+        <v>65</v>
+      </c>
+      <c r="H13" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
